--- a/jogos_2024-12-19.xlsx
+++ b/jogos_2024-12-19.xlsx
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,25 +1159,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CODM Meknès</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>3.9</v>
       </c>
       <c r="M6" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
@@ -1209,59 +1209,59 @@
         <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['45+3', '81', '83']</t>
+          <t>['5', '63']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '40', '45+1', '55']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.08</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.37</v>
+        <v>1.23</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45645.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,48 +1288,48 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.5</v>
@@ -1344,53 +1344,53 @@
         <v>1.29</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['5', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['20', '40', '45+1', '55']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.71</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.23</v>
+        <v>1.73</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45645.5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,48 +1417,48 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>CODM Meknès</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="R8" t="n">
         <v>1.5</v>
@@ -1467,59 +1467,59 @@
         <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['45+3', '81', '83']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.08</v>
       </c>
-      <c r="W8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.73</v>
+        <v>2.37</v>
       </c>
       <c r="AI8" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.38</v>
+        <v>5.5</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45645.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="M11" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>2.63</v>
       </c>
       <c r="T11" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="X11" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['25', '73', '90+6']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45645.625</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P12" t="n">
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U12" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['25', '73', '90+6']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45645.625</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="I15" t="n">
-        <v>3</v>
-      </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="U15" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.69</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.17</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['35']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['36', '39', '45', '49', '52']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['7']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45645.71875</v>
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
       <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P16" t="n">
         <v>2.3</v>
       </c>
-      <c r="M16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="Q16" t="n">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['36', '39', '45', '49', '52']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI16" t="n">
         <v>1.67</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['35']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AJ16" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45645.71875</v>
